--- a/MainTop/01.04.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/01.04.2026 Таня ВБ/print_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\01.04.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9079BD-FE9B-406C-BA54-22000EEE4F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3782A0-19E6-4A2E-9D4F-FF43BF0B5D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -551,9 +551,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -596,6 +598,12 @@
         <bgColor rgb="FFFFA07A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -624,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -635,6 +643,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2766,100 +2775,100 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="5" t="s">
+      <c r="A131" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B131" s="5">
+      <c r="B131" s="8">
         <v>36</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C131" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D131" s="5" t="s">
+      <c r="D131" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="5" t="s">
+      <c r="A132" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B132" s="5">
+      <c r="B132" s="8">
         <v>24</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="C132" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="D132" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="5" t="s">
+      <c r="A133" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B133" s="5">
+      <c r="B133" s="8">
         <v>24</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="C133" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D133" s="5" t="s">
+      <c r="D133" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="5" t="s">
+      <c r="A134" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B134" s="5">
+      <c r="B134" s="8">
         <v>16</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C134" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="D134" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="5" t="s">
+      <c r="A135" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B135" s="5">
+      <c r="B135" s="8">
         <v>16</v>
       </c>
-      <c r="C135" s="5" t="s">
+      <c r="C135" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D135" s="5" t="s">
+      <c r="D135" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="5" t="s">
+      <c r="A136" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B136" s="5">
+      <c r="B136" s="8">
         <v>16</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C136" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="D136" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="5" t="s">
+      <c r="A137" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B137" s="5">
-        <v>12</v>
-      </c>
-      <c r="C137" s="5" t="s">
+      <c r="B137" s="8">
+        <v>4</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D137" s="5" t="s">
+      <c r="D137" s="8" t="s">
         <v>6</v>
       </c>
     </row>
